--- a/prep_and_checklists/ShopMy  /PREP_REQ_ShopMy  _Tuesday, December 9, 2025  _0.xlsx
+++ b/prep_and_checklists/ShopMy  /PREP_REQ_ShopMy  _Tuesday, December 9, 2025  _0.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidcuvin/purveyor_project/prep_and_checklists/ShopMy  /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30006F74-E886-8F44-99E1-F1CDE301D713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DEAFF92-307F-2648-B4DC-13604F3A892B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="920" windowWidth="29940" windowHeight="17600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-340" yWindow="1680" windowWidth="29940" windowHeight="17600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Prep Req" sheetId="1" r:id="rId1"/>
+    <sheet name="Order Guide" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
   <si>
     <t>EVENT PREP 12-05-2025</t>
   </si>
@@ -71,6 +72,57 @@
   </si>
   <si>
     <t>cacio e pepe arancini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event:Westman Atelier   Date: Wednesday, March 25, 2026  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Before Wednesday, March 25, 2026  </t>
+  </si>
+  <si>
+    <t>Ingredient</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>hamachi</t>
+  </si>
+  <si>
+    <t>Event:ShopMy   Date: Monday, March 23, 2026  </t>
+  </si>
+  <si>
+    <t>Before Monday, March 23, 2026  </t>
+  </si>
+  <si>
+    <t>black diamond kaluga shrenckii caviar per 1kg</t>
+  </si>
+  <si>
+    <t>nebraska prime nature source beef boneless 0x1 strip</t>
+  </si>
+  <si>
+    <t>lobstermeat</t>
+  </si>
+  <si>
+    <t>1 x loin</t>
+  </si>
+  <si>
+    <t>frozen, gased</t>
+  </si>
+  <si>
+    <t>2lbs</t>
+  </si>
+  <si>
+    <t>frozen</t>
+  </si>
+  <si>
+    <t>1/2 x 200g tin</t>
   </si>
 </sst>
 </file>
@@ -80,7 +132,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dddd\ m/d"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,7 +172,27 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -128,10 +200,13 @@
     </font>
     <font>
       <sz val="14"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -144,8 +219,20 @@
         <bgColor rgb="FFD8D8D8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95B3D7"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -205,11 +292,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -237,28 +339,43 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -477,7 +594,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V979"/>
+  <dimension ref="A1:V977"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="42.33203125" style="2" customWidth="1"/>
@@ -492,14 +609,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -518,22 +635,22 @@
       <c r="V1" s="1"/>
     </row>
     <row r="2" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>6</v>
       </c>
       <c r="G2" s="3"/>
@@ -554,19 +671,19 @@
       <c r="V2" s="3"/>
     </row>
     <row r="3" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="13"/>
+      <c r="E3" s="12"/>
       <c r="F3" s="7"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -586,19 +703,19 @@
       <c r="V3" s="3"/>
     </row>
     <row r="4" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="14"/>
+      <c r="E4" s="13"/>
       <c r="F4" s="4"/>
       <c r="G4" s="5"/>
       <c r="H4" s="3"/>
@@ -618,19 +735,19 @@
       <c r="V4" s="3"/>
     </row>
     <row r="5" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="12"/>
+      <c r="E5" s="11"/>
       <c r="F5" s="6"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -650,19 +767,19 @@
       <c r="V5" s="3"/>
     </row>
     <row r="6" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="12"/>
+      <c r="E6" s="11"/>
       <c r="F6" s="8"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -682,19 +799,19 @@
       <c r="V6" s="3"/>
     </row>
     <row r="7" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="13"/>
+      <c r="E7" s="12"/>
       <c r="F7" s="7"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
@@ -714,11 +831,11 @@
       <c r="V7" s="3"/>
     </row>
     <row r="8" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
       <c r="F8" s="4"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
@@ -738,12 +855,6 @@
       <c r="V8" s="3"/>
     </row>
     <row r="9" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="4"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
@@ -762,12 +873,6 @@
       <c r="V9" s="3"/>
     </row>
     <row r="10" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="4"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
@@ -786,12 +891,6 @@
       <c r="V10" s="3"/>
     </row>
     <row r="11" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="4"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
@@ -810,12 +909,6 @@
       <c r="V11" s="3"/>
     </row>
     <row r="12" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="6"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -834,12 +927,6 @@
       <c r="V12" s="3"/>
     </row>
     <row r="13" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="4"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
@@ -858,12 +945,6 @@
       <c r="V13" s="3"/>
     </row>
     <row r="14" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="4"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
@@ -882,12 +963,6 @@
       <c r="V14" s="3"/>
     </row>
     <row r="15" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="6"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
@@ -906,12 +981,6 @@
       <c r="V15" s="3"/>
     </row>
     <row r="16" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="6"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
@@ -929,13 +998,7 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
     </row>
-    <row r="17" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="6"/>
+    <row r="17" spans="7:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
@@ -953,13 +1016,7 @@
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
     </row>
-    <row r="18" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="6"/>
+    <row r="18" spans="7:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
@@ -977,13 +1034,7 @@
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
     </row>
-    <row r="19" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="6"/>
+    <row r="19" spans="7:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
@@ -1001,13 +1052,7 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
     </row>
-    <row r="20" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="4"/>
+    <row r="20" spans="7:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
@@ -1025,13 +1070,7 @@
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
     </row>
-    <row r="21" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="4"/>
+    <row r="21" spans="7:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
@@ -1049,13 +1088,7 @@
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
     </row>
-    <row r="22" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="4"/>
+    <row r="22" spans="7:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
@@ -1073,13 +1106,7 @@
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
     </row>
-    <row r="23" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="4"/>
+    <row r="23" spans="7:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
@@ -1097,13 +1124,7 @@
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
     </row>
-    <row r="24" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="4"/>
+    <row r="24" spans="7:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
@@ -1121,13 +1142,7 @@
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
     </row>
-    <row r="25" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="4"/>
+    <row r="25" spans="7:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
@@ -1145,13 +1160,7 @@
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
     </row>
-    <row r="26" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="4"/>
+    <row r="26" spans="7:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
@@ -1169,13 +1178,7 @@
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
     </row>
-    <row r="27" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="4"/>
+    <row r="27" spans="7:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
@@ -1193,13 +1196,7 @@
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
     </row>
-    <row r="28" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="4"/>
+    <row r="28" spans="7:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
@@ -1217,13 +1214,7 @@
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
     </row>
-    <row r="29" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="4"/>
+    <row r="29" spans="7:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
@@ -1241,13 +1232,7 @@
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
     </row>
-    <row r="30" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="4"/>
+    <row r="30" spans="7:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
@@ -1265,13 +1250,7 @@
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
     </row>
-    <row r="31" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="4"/>
+    <row r="31" spans="7:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
@@ -1289,13 +1268,7 @@
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
     </row>
-    <row r="32" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="12"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="4"/>
+    <row r="32" spans="7:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
@@ -1313,13 +1286,7 @@
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
     </row>
-    <row r="33" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="12"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="6"/>
+    <row r="33" spans="7:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
@@ -1337,13 +1304,7 @@
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
     </row>
-    <row r="34" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="12"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="9"/>
+    <row r="34" spans="7:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -1361,13 +1322,7 @@
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
     </row>
-    <row r="35" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="12"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="9"/>
+    <row r="35" spans="7:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
@@ -1385,13 +1340,7 @@
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
     </row>
-    <row r="36" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="12"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="9"/>
+    <row r="36" spans="7:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -1409,13 +1358,7 @@
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
     </row>
-    <row r="37" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="12"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="9"/>
+    <row r="37" spans="7:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
@@ -1433,13 +1376,7 @@
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
     </row>
-    <row r="38" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="12"/>
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="9"/>
+    <row r="38" spans="7:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
@@ -1457,13 +1394,7 @@
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
     </row>
-    <row r="39" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="12"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="9"/>
+    <row r="39" spans="7:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -1481,224 +1412,31 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
     </row>
-    <row r="40" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="12"/>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3"/>
-      <c r="O40" s="3"/>
-      <c r="P40" s="3"/>
-      <c r="Q40" s="3"/>
-      <c r="R40" s="3"/>
-      <c r="S40" s="3"/>
-      <c r="T40" s="3"/>
-      <c r="U40" s="3"/>
-      <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="12"/>
-      <c r="B41" s="12"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3"/>
-      <c r="O41" s="3"/>
-      <c r="P41" s="3"/>
-      <c r="Q41" s="3"/>
-      <c r="R41" s="3"/>
-      <c r="S41" s="3"/>
-      <c r="T41" s="3"/>
-      <c r="U41" s="3"/>
-      <c r="V41" s="3"/>
-    </row>
-    <row r="42" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="12"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="9"/>
-    </row>
-    <row r="43" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="12"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="9"/>
-    </row>
-    <row r="44" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="12"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="9"/>
-    </row>
-    <row r="45" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="12"/>
-      <c r="B45" s="12"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="9"/>
-    </row>
-    <row r="46" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="12"/>
-      <c r="B46" s="12"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="9"/>
-    </row>
-    <row r="47" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="12"/>
-      <c r="B47" s="12"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="9"/>
-    </row>
-    <row r="48" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="12"/>
-      <c r="B48" s="12"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="9"/>
-    </row>
-    <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="12"/>
-      <c r="B49" s="12"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="9"/>
-    </row>
-    <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="12"/>
-      <c r="B50" s="12"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="9"/>
-    </row>
-    <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="12"/>
-      <c r="B51" s="12"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="9"/>
-    </row>
-    <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="12"/>
-      <c r="B52" s="12"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="9"/>
-    </row>
-    <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="12"/>
-      <c r="B53" s="12"/>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="9"/>
-    </row>
-    <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="12"/>
-      <c r="B54" s="12"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="9"/>
-    </row>
-    <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="12"/>
-      <c r="B55" s="12"/>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="9"/>
-    </row>
-    <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="12"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="9"/>
-    </row>
-    <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="12"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="9"/>
-    </row>
-    <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="12"/>
-      <c r="B58" s="12"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="9"/>
-    </row>
-    <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="12"/>
-      <c r="B59" s="12"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="9"/>
-    </row>
-    <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="12"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="12"/>
-      <c r="E60" s="12"/>
-      <c r="F60" s="9"/>
-    </row>
-    <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="12"/>
-      <c r="B61" s="12"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="12"/>
-      <c r="E61" s="12"/>
-      <c r="F61" s="9"/>
-    </row>
-    <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="12"/>
-      <c r="B62" s="12"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="12"/>
-      <c r="E62" s="12"/>
-      <c r="F62" s="9"/>
-    </row>
-    <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" spans="7:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="7:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="7:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="7:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="7:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" spans="7:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="7:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="7:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="7:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -2612,8 +2350,6 @@
     <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
@@ -2621,4 +2357,127 @@
   <pageMargins left="0.75" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{557F3017-B967-3E48-9874-4D9A984EFED0}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="3" max="3" width="27.33203125" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A1" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+    </row>
+    <row r="2" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A2" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+    </row>
+    <row r="3" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A3" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="19" x14ac:dyDescent="0.2">
+      <c r="A4" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="19" x14ac:dyDescent="0.2">
+      <c r="A5" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="18"/>
+    </row>
+    <row r="6" spans="1:4" ht="19" x14ac:dyDescent="0.2">
+      <c r="A6" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+    </row>
+    <row r="7" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A7" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+    </row>
+    <row r="8" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A8" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+    </row>
+    <row r="9" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A9" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="19" x14ac:dyDescent="0.2">
+      <c r="A10" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>